--- a/JP (Exclude Game)/Data/god_talk.xlsx
+++ b/JP (Exclude Game)/Data/god_talk.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="216">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t xml:space="preserve">そう、どうせあなたも私を裏切るのね</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うみみやぁ！</t>
   </si>
   <si>
     <t xml:space="preserve">おやおや、歓迎するよ。お前を退屈させないよう気を付けよう。</t>
@@ -498,7 +495,7 @@
   </si>
   <si>
     <t xml:space="preserve">みじめなブタども。
-マニ？その名を再び口にしたらミンチよ、子猫ちゃん。
+マニ？その名を再び口にしたらミンチよ、仔猫ちゃん。
 前の下僕は、八つ裂きにしてシルフ達の餌にしたわ。髪型がちょっと気に食わなかったから。アハハ！
 私の子供達は風の声、何事にも縛られてはいけない。オマエもよ。</t>
   </si>
@@ -824,6 +821,39 @@
   <si>
     <t xml:space="preserve">お兄さんの元へ行くのですか？粗相をしては駄目ですよ。
 あらあら、お兄さんがあなたを気に入るといいけど…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愚かな制度だが、今日は祝ってやろう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自ら縛られるなんて、馬鹿ね、オマエは。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">汝ら二人を我が名において祝福しよう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幸せになってね！ね！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フハハハハハハ！！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">べ、別に嫉妬なんかしてないんだからね！お、おめでとう…バカ…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ずっと大切に…離さずに…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お前を祝福するよ。今日は悪戯は止めておこう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まあ、とてもおめでたいわ！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おめでとう、とても良い進捗だね。</t>
   </si>
 </sst>
 </file>
@@ -993,9 +1023,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1342080</xdr:colOff>
+      <xdr:colOff>1341720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1005,7 +1035,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1342080" cy="154800"/>
+          <a:ext cx="1341720" cy="154440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1038,9 +1068,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1342080</xdr:colOff>
+      <xdr:colOff>1341720</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>155520</xdr:rowOff>
+      <xdr:rowOff>155160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1050,7 +1080,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1342080" cy="155520"/>
+          <a:ext cx="1341720" cy="155160"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1080,9 +1110,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1148760</xdr:colOff>
+      <xdr:colOff>1148400</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:rowOff>151560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1092,7 +1122,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1148760" cy="151920"/>
+          <a:ext cx="1148400" cy="151560"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1327,742 +1357,786 @@
         <v>23</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="N8" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="N9" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="N12" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="M13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="N13" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="N14" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="86.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="M15" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="N15" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="5" t="s">
+      <c r="M16" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="N16" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="I17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="I18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="G20" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="I20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C21" s="7"/>
       <c r="G21" s="7"/>
       <c r="L21" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="M21" s="7" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>205</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
